--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0085.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0085.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Không. Ta định diễn vào tháng sau.</t>
+          <t>Không. Tao định diễn vào tháng sau.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Vậy còn đang đứng đây làm gì nữa? Đi tìm Nado bảo hắn viết hết ra đi! Ta muốn bắt đầu diễn tập ngay lập tức!</t>
+          <t>Vậy còn đang đứng đây làm gì nữa? Đi tìm Nado bảo hắn viết hết ra đi! Tao muốn bắt đầu diễn tập ngay lập tức!</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Đủ làm cậu giật mình tỉnh giấc chưa?</t>
+          <t>Đủ làm mày giật mình tỉnh giấc chưa?</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Thực ra, đầu ta đang đầy ý tưởng, nhưng không tài nào tập trung vào một cái để bắt đầu câu chuyện được.</t>
+          <t>Thực ra, đầu tao đang đầy ý tưởng, nhưng không tài nào tập trung vào một cái để bắt đầu câu chuyện được.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Ta có một số tài liệu gốc cho cậu đây.</t>
+          <t>Tao có một số tài liệu gốc cho cậu đây.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Một con sứa có thể biến thành người à? Than ôi, khả năng đó cũng chẳng khác gì việc ta làm theo lời ngươi đâu.</t>
+          <t>Một con sứa có thể biến thành người à? Than ôi, khả năng đó cũng chẳng khác gì việc tao làm theo lời mày đâu.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ta đã nghĩ về chuyện đó, nhưng giờ thì không nữa.</t>
+          <t>Tao đã nghĩ về chuyện đó, nhưng giờ thì không nữa.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Bọn Tín Đồ có thể đuổi ta đi, nhưng chúng không thể trục xuất được pháo hoa của ta. Hãy tưởng tượng mặt chúng khi thấy pháo hoa CỦA TA thắp sáng bầu trời...</t>
+          <t>Bọn Tín Đồ có thể đuổi tao đi, nhưng chúng không thể trục xuất được pháo hoa của tao. Hãy tưởng tượng mặt chúng khi thấy pháo hoa CỦA TA thắp sáng bầu trời...</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Haha! Chỉ nghĩ thôi là mũi ta đã ngứa ngáy rồi…</t>
+          <t>Haha! Chỉ nghĩ thôi là mũi tao đã ngứa ngáy rồi…</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Ta không thể làm gì nhiều cho họ. Nhưng ít nhất, ta có thể cho họ một đêm ngủ ngon.</t>
+          <t>Tao không thể làm gì nhiều cho họ. Nhưng ít nhất, tao có thể cho họ một đêm ngủ ngon.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Lord Fenrico mất tích, còn thái độ của Hội thì... thật đáng ngờ. Ta sợ tụi mình sẽ bị giết ngay khi đặt chân về đó.</t>
+          <t>Lord Fenrico mất tích, còn thái độ của Hội thì... thật đáng ngờ. Tao sợ tụi mình sẽ bị giết ngay khi đặt chân về đó.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Ta không quan tâm! Ta sẽ về ngay bây giờ!</t>
+          <t>Tao không quan tâm! Tao sẽ về ngay bây giờ!</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Ta tin rằng mọi người đã bắt đầu nhận ra rằng đằng sau chúng ta, luôn có đôi cánh ân sủng sẵn sàng nâng bước ta tiến về phía trước.</t>
+          <t>Tao tin rằng mọi người đã bắt đầu nhận ra rằng đằng sau chúng ta, luôn có đôi cánh ân sủng sẵn sàng nâng bước ta tiến về phía trước.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Được rồi, hôm nay là ngày đó rồi! Trước khi sếp quay lại, ta phải đi săn con Tubpup phiên bản giới hạn thôi!</t>
+          <t>Được rồi, hôm nay là ngày đó rồi! Trước khi sếp quay lại, tao phải đi săn con Tubpup phiên bản giới hạn thôi!</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tớ nhớ vị anh hùng này. {Male=Ông ấy;Female=Bà ấy} từng sát cánh cùng Thánh Nữ và các chiến binh khác, cùng nhau đánh bại Threnodian.</t>
+          <t>Tớ nhớ vị anh hùng này. {Male=He;Female=She} từng sát cánh cùng Thánh Nữ và các chiến binh khác, cùng nhau đánh bại Threnodian.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female=Cô ấy} là Anh Hùng của Ragunna. Dù {Male=anh ấy;Female=cô ấy} có hành động hơi… *thở dài*… Thôi, cứ bình tĩnh đã.</t>
+          <t>{Male=he;Female=she} là Anh Hùng của Ragunna. Dù {Male=he;Female=she} có hành động hơi… *thở dài*… Thôi, cứ bình tĩnh đã.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>À, Rover của Rinascita. Hôm nay có việc gì mà tìm đến ta thế?</t>
+          <t>À, Vận Mệnh Giả của Rinascita. Hôm nay có việc gì mà tìm đến ta thế?</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Thở dài... Nhận được thông báo rồi… Ta phải quay về Septimont kiểm tra sức khỏe. Xui một chút là có khi còn phải giải nghệ luôn.</t>
+          <t>Thở dài... Nhận được thông báo rồi… Tao phải quay về Septimont kiểm tra sức khỏe. Xui một chút là có khi còn phải giải nghệ luôn.</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Đừng cố tỏ ra cứng rắn thế. Ngay cả {Male=quý ông;Female=tiểu thư} này cũng thấy nụ cười của cậu gượng ép.</t>
+          <t>Đừng cố tỏ ra cứng rắn thế. Ngay cả {Male=gentleman;Female=lady} này cũng thấy nụ cười của cậu gượng ép.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Ngươi! Nhắc lại cho ta nghe! Xem ngươi có thực sự nghe không đấy.</t>
+          <t>Mày! Nhắc lại cho tao nghe! Xem mày có thực sự nghe không đấy.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>SAI BÉT! Còn lâu mới đúng! Cậu có nghe được một chữ nào không vậy?!</t>
+          <t>SAI BÉT! Còn lâu mới đúng! Mày có nghe được một chữ nào không vậy?!</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Ephor Augusta mạnh thật đấy, nhưng không phải mạnh đến thế. Đó chính là điều ta muốn nói.</t>
+          <t>Ephor Augusta mạnh thật đấy, nhưng không phải mạnh đến thế. Đó chính là điều tao muốn nói.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Ephor Augusta mạnh thật đấy, nhưng không phải mạnh đến thế. Đó chính là điều ta muốn nói.</t>
+          <t>Ephor Augusta mạnh thật đấy, nhưng không phải mạnh đến thế. Đó chính là điều tao muốn nói.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
